--- a/exports/trend_1d/BANKNIFTY_full_report.xlsx
+++ b/exports/trend_1d/BANKNIFTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>19865.9</v>
+        <v>19329.95</v>
       </c>
       <c r="I2" t="n">
         <v>19636.5383055833</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.61458333333333</v>
+        <v>18.61458333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>3.28</v>
+        <v>0.49</v>
       </c>
       <c r="L2" t="n">
         <v>0.91</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42063</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>19691.2</v>
+        <v>20008.1</v>
       </c>
       <c r="I3" t="n">
         <v>19788.52675910412</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.87</v>
+        <v>-3.51</v>
       </c>
       <c r="L3" t="n">
-        <v>3.28</v>
+        <v>3.81</v>
       </c>
       <c r="M3" t="n">
         <v>0.27</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H4" t="n">
-        <v>18811.15</v>
+        <v>18606.35</v>
       </c>
       <c r="I4" t="n">
         <v>18706.54063335179</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.98</v>
+        <v>-7.01</v>
       </c>
       <c r="L4" t="n">
-        <v>6.59</v>
+        <v>7.33</v>
       </c>
       <c r="M4" t="n">
         <v>0.01</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.98</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>18449.2</v>
+        <v>18721.35</v>
       </c>
       <c r="I5" t="n">
         <v>18666.57010944823</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K5" t="n">
-        <v>0.84</v>
+        <v>-0.62</v>
       </c>
       <c r="L5" t="n">
         <v>2.32</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.53</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H6" t="n">
-        <v>17977.3</v>
+        <v>17721.4</v>
       </c>
       <c r="I6" t="n">
         <v>17817.91506118178</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.97</v>
+        <v>-5.34</v>
       </c>
       <c r="L6" t="n">
-        <v>4.21</v>
+        <v>6.16</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42177.37402777778</v>
+        <v>42178.37403935185</v>
       </c>
       <c r="H7" t="n">
-        <v>18334.5</v>
+        <v>18391.35</v>
       </c>
       <c r="I7" t="n">
         <v>18374.14515097764</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19.37402777777778</v>
+        <v>20.37403935185185</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.46</v>
+        <v>-3.78</v>
       </c>
       <c r="L7" t="n">
-        <v>3.95</v>
+        <v>4.39</v>
       </c>
       <c r="M7" t="n">
         <v>0.63</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42209.37398148148</v>
+        <v>42212.34644675926</v>
       </c>
       <c r="H8" t="n">
-        <v>18635.85</v>
+        <v>18213.05</v>
       </c>
       <c r="I8" t="n">
         <v>18362.22888400928</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30.99994212962963</v>
+        <v>33.97240740740741</v>
       </c>
       <c r="K8" t="n">
-        <v>1.33</v>
+        <v>-0.97</v>
       </c>
       <c r="L8" t="n">
         <v>3.1</v>
@@ -897,7 +992,7 @@
         <v>2.23</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="O8" t="n">
         <v>0.31</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42265.34336805555</v>
+        <v>42268.34334490741</v>
       </c>
       <c r="H9" t="n">
-        <v>17409.15</v>
+        <v>17542.9</v>
       </c>
       <c r="I9" t="n">
         <v>17424.75262662751</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>52.99692129629629</v>
+        <v>55.99689814814815</v>
       </c>
       <c r="K9" t="n">
-        <v>4.41</v>
+        <v>3.68</v>
       </c>
       <c r="L9" t="n">
         <v>4.89</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42312.36326388889</v>
+        <v>42313.35915509259</v>
       </c>
       <c r="H10" t="n">
-        <v>17221.05</v>
+        <v>16995.1</v>
       </c>
       <c r="I10" t="n">
         <v>17060.32007252192</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44.01991898148148</v>
+        <v>45.01581018518519</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.83</v>
+        <v>-3.12</v>
       </c>
       <c r="L10" t="n">
         <v>5.1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42369.38541666666</v>
+        <v>42370.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>16922.2</v>
+        <v>17039.25</v>
       </c>
       <c r="I11" t="n">
         <v>17031.49433072185</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>56.02626157407408</v>
+        <v>57.02626157407408</v>
       </c>
       <c r="K11" t="n">
-        <v>0.43</v>
+        <v>-0.26</v>
       </c>
       <c r="L11" t="n">
         <v>2.96</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>4.03</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42375.38541666666</v>
+        <v>42376.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>16433.15</v>
+        <v>16073.85</v>
       </c>
       <c r="I12" t="n">
         <v>16352.50434702727</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.56</v>
+        <v>-5.67</v>
       </c>
       <c r="L12" t="n">
-        <v>3.88</v>
+        <v>5.81</v>
       </c>
       <c r="M12" t="n">
-        <v>0.43</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>2.58</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42430.38541666666</v>
+        <v>42431.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>14412.9</v>
+        <v>15092.45</v>
       </c>
       <c r="I13" t="n">
         <v>14675.59124052553</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" t="n">
-        <v>10.33</v>
+        <v>6.11</v>
       </c>
       <c r="L13" t="n">
         <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6</v>
+        <v>2.48</v>
       </c>
       <c r="N13" t="n">
-        <v>3.39</v>
+        <v>4.71</v>
       </c>
       <c r="O13" t="n">
         <v>-2.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42636.38541666666</v>
+        <v>42639.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>19901.8</v>
+        <v>19591.75</v>
       </c>
       <c r="I14" t="n">
         <v>19745.14153699916</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K14" t="n">
-        <v>31.87</v>
+        <v>29.81</v>
       </c>
       <c r="L14" t="n">
         <v>2.15</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>4.66</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42667.38541666666</v>
+        <v>42668.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>19807.9</v>
+        <v>19834.9</v>
       </c>
       <c r="I15" t="n">
         <v>19821.65918218907</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1</v>
+        <v>-1.24</v>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
         <v>0.65</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.13</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42692.38541666666</v>
+        <v>42695.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>18959.05</v>
+        <v>18446.4</v>
       </c>
       <c r="I16" t="n">
         <v>18786.20838079411</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.42</v>
+        <v>-7</v>
       </c>
       <c r="L16" t="n">
         <v>8.529999999999999</v>
@@ -1353,7 +1544,7 @@
         <v>6.31</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0.14</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.98</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42745.38541666666</v>
+        <v>42746.41388888889</v>
       </c>
       <c r="H17" t="n">
-        <v>18409.6</v>
+        <v>18830</v>
       </c>
       <c r="I17" t="n">
         <v>18512.94916173303</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>50</v>
+        <v>51.02847222222222</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>-2.08</v>
       </c>
       <c r="L17" t="n">
         <v>3.41</v>
@@ -1410,7 +1613,7 @@
         <v>0.98</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
         <v>-2.7</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.86</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42956.38541666666</v>
+        <v>42957.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>24374.6</v>
+        <v>24217.35</v>
       </c>
       <c r="I18" t="n">
         <v>24363.07927678764</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>209.9715277777778</v>
+        <v>210.9715277777778</v>
       </c>
       <c r="K18" t="n">
-        <v>29.45</v>
+        <v>28.61</v>
       </c>
       <c r="L18" t="n">
         <v>1.67</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>3.14</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42993.38541666666</v>
+        <v>42996.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>24844.3</v>
+        <v>25046.9</v>
       </c>
       <c r="I19" t="n">
         <v>24946.43337326291</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.59</v>
+        <v>-3.43</v>
       </c>
       <c r="L19" t="n">
-        <v>3.21</v>
+        <v>3.67</v>
       </c>
       <c r="M19" t="n">
         <v>0.6</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>2.77</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42999.38541666666</v>
+        <v>43000.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>24799.25</v>
+        <v>24368.85</v>
       </c>
       <c r="I20" t="n">
         <v>24411.92686292195</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.99</v>
+        <v>-2.71</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>2.82</v>
       </c>
       <c r="M20" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="N20" t="n">
-        <v>0.66</v>
+        <v>1.74</v>
       </c>
       <c r="O20" t="n">
         <v>0.82</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>3.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43032.38541666666</v>
+        <v>43033.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>24222.15</v>
+        <v>25035.9</v>
       </c>
       <c r="I21" t="n">
         <v>24728.46634518021</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6</v>
+        <v>-2.74</v>
       </c>
       <c r="L21" t="n">
-        <v>2.09</v>
+        <v>3.24</v>
       </c>
       <c r="M21" t="n">
-        <v>0.61</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>3.36</v>
       </c>
       <c r="O21" t="n">
         <v>-1.74</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.98</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43070.38541666666</v>
+        <v>43073.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>25191.95</v>
+        <v>25075.1</v>
       </c>
       <c r="I22" t="n">
         <v>25173.14622574126</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>0.62</v>
+        <v>0.16</v>
       </c>
       <c r="L22" t="n">
         <v>1.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>3.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43112.38541666666</v>
+        <v>43115.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>25749.05</v>
+        <v>26069.2</v>
       </c>
       <c r="I23" t="n">
         <v>25759.85793629584</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.69</v>
+        <v>-3.96</v>
       </c>
       <c r="L23" t="n">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="M23" t="n">
         <v>1.27</v>
       </c>
       <c r="N23" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
         <v>-0.46</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.01</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43132.38541666666</v>
+        <v>43133.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>27220.7</v>
+        <v>26451.15</v>
       </c>
       <c r="I24" t="n">
         <v>26625.57298750375</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>4.42</v>
+        <v>1.47</v>
       </c>
       <c r="L24" t="n">
         <v>0.87</v>
       </c>
       <c r="M24" t="n">
-        <v>0.49</v>
+        <v>0.75</v>
       </c>
       <c r="N24" t="n">
-        <v>0.83</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
         <v>1.24</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.22</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43195.38541666666</v>
+        <v>43196.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>24759.8</v>
+        <v>24873.15</v>
       </c>
       <c r="I25" t="n">
         <v>24809.88597850483</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>6.39</v>
+        <v>5.97</v>
       </c>
       <c r="L25" t="n">
         <v>2.14</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.17</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43238.38541666666</v>
+        <v>43241.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>25875.6</v>
+        <v>25750.8</v>
       </c>
       <c r="I26" t="n">
         <v>25784.52098825686</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>4.03</v>
+        <v>3.53</v>
       </c>
       <c r="L26" t="n">
         <v>1.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.06</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43250.38541666666</v>
+        <v>43251.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>26327.8</v>
+        <v>26956.2</v>
       </c>
       <c r="I27" t="n">
         <v>26657.89921160479</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.24</v>
+        <v>-4.68</v>
       </c>
       <c r="L27" t="n">
-        <v>3.74</v>
+        <v>5.49</v>
       </c>
       <c r="M27" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="N27" t="n">
-        <v>1.3</v>
+        <v>2.39</v>
       </c>
       <c r="O27" t="n">
         <v>-0.48</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.06</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43347.38541666666</v>
+        <v>43348.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>27430.75</v>
+        <v>27376.05</v>
       </c>
       <c r="I28" t="n">
         <v>27430.25093995093</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K28" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="L28" t="n">
         <v>3.32</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>3.27</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43418.38541666666</v>
+        <v>43419.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>25930.15</v>
+        <v>26154.75</v>
       </c>
       <c r="I29" t="n">
         <v>26065.12818661689</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K29" t="n">
-        <v>5.28</v>
+        <v>4.46</v>
       </c>
       <c r="L29" t="n">
         <v>0.65</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H30" t="n">
-        <v>27115.3</v>
+        <v>26653.05</v>
       </c>
       <c r="I30" t="n">
         <v>26690.58270841893</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>70.61458333333333</v>
+        <v>73.61458333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>3.67</v>
+        <v>1.91</v>
       </c>
       <c r="L30" t="n">
         <v>2.13</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.19</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H31" t="n">
-        <v>27043.9</v>
+        <v>27554.05</v>
       </c>
       <c r="I31" t="n">
         <v>27501.97299760513</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.47</v>
+        <v>-3.38</v>
       </c>
       <c r="L31" t="n">
         <v>3.51</v>
@@ -2208,7 +2579,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
         <v>-1.7</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.61</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H32" t="n">
-        <v>29288.2</v>
+        <v>28994.4</v>
       </c>
       <c r="I32" t="n">
         <v>29258.81856120917</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K32" t="n">
-        <v>6.29</v>
+        <v>5.23</v>
       </c>
       <c r="L32" t="n">
         <v>2.16</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.88</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H33" t="n">
-        <v>29450.15</v>
+        <v>30759.7</v>
       </c>
       <c r="I33" t="n">
         <v>29988.82442651824</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.57</v>
+        <v>-6.09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>6.32</v>
       </c>
       <c r="M33" t="n">
-        <v>0.33</v>
+        <v>2.65</v>
       </c>
       <c r="N33" t="n">
-        <v>2.06</v>
+        <v>4.45</v>
       </c>
       <c r="O33" t="n">
         <v>-1</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.2</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H34" t="n">
-        <v>30430.6</v>
+        <v>29770.35</v>
       </c>
       <c r="I34" t="n">
         <v>30400.05159829324</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.07</v>
+        <v>-3.22</v>
       </c>
       <c r="L34" t="n">
-        <v>2.11</v>
+        <v>3.43</v>
       </c>
       <c r="M34" t="n">
         <v>0.44</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.26</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H35" t="n">
-        <v>26757.65</v>
+        <v>28981.55</v>
       </c>
       <c r="I35" t="n">
         <v>28414.34630682955</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>10.12</v>
+        <v>2.65</v>
       </c>
       <c r="L35" t="n">
         <v>2.6</v>
@@ -2436,7 +2855,7 @@
         <v>2.62</v>
       </c>
       <c r="N35" t="n">
-        <v>3.68</v>
+        <v>8.31</v>
       </c>
       <c r="O35" t="n">
         <v>-2.17</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.59</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43741</v>
+        <v>43742</v>
       </c>
       <c r="H36" t="n">
-        <v>28414.1</v>
+        <v>27731.85</v>
       </c>
       <c r="I36" t="n">
         <v>27802.68386732126</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.96</v>
+        <v>-4.31</v>
       </c>
       <c r="L36" t="n">
         <v>7.78</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.03</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H37" t="n">
-        <v>30219.85</v>
+        <v>30609.6</v>
       </c>
       <c r="I37" t="n">
         <v>30401.25744725046</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.970000000000001</v>
+        <v>-10.38</v>
       </c>
       <c r="L37" t="n">
-        <v>10.37</v>
+        <v>10.7</v>
       </c>
       <c r="M37" t="n">
         <v>1.02</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.11</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H38" t="n">
-        <v>32069.25</v>
+        <v>31237.15</v>
       </c>
       <c r="I38" t="n">
         <v>31397.92036308815</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K38" t="n">
-        <v>4.77</v>
+        <v>2.05</v>
       </c>
       <c r="L38" t="n">
         <v>1.95</v>
       </c>
       <c r="M38" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O38" t="n">
         <v>1.29</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43872</v>
+        <v>43873</v>
       </c>
       <c r="H39" t="n">
-        <v>31300.6</v>
+        <v>31492.9</v>
       </c>
       <c r="I39" t="n">
         <v>31356.42633183336</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="L39" t="n">
         <v>3.55</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.31</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H40" t="n">
-        <v>30187</v>
+        <v>29147.15</v>
       </c>
       <c r="I40" t="n">
         <v>30136.69203295323</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.15</v>
+        <v>-7.45</v>
       </c>
       <c r="L40" t="n">
-        <v>5.01</v>
+        <v>7.75</v>
       </c>
       <c r="M40" t="n">
-        <v>0.89</v>
+        <v>2.27</v>
       </c>
       <c r="N40" t="n">
-        <v>1.58</v>
+        <v>3.44</v>
       </c>
       <c r="O40" t="n">
         <v>0.61</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.68</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H41" t="n">
-        <v>19297.25</v>
+        <v>19959.9</v>
       </c>
       <c r="I41" t="n">
         <v>19920.43478177684</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K41" t="n">
-        <v>33.79</v>
+        <v>31.52</v>
       </c>
       <c r="L41" t="n">
         <v>2.21</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.84</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H42" t="n">
-        <v>21640.05</v>
+        <v>21072.1</v>
       </c>
       <c r="I42" t="n">
         <v>21136.52852938541</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K42" t="n">
-        <v>8.42</v>
+        <v>5.57</v>
       </c>
       <c r="L42" t="n">
         <v>2.27</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.56</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44067</v>
+        <v>44068</v>
       </c>
       <c r="H43" t="n">
-        <v>22833</v>
+        <v>23092.15</v>
       </c>
       <c r="I43" t="n">
         <v>23085.8063187059</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.359999999999999</v>
+        <v>-9.59</v>
       </c>
       <c r="L43" t="n">
-        <v>8.66</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
         <v>1.05</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H44" t="n">
-        <v>22744.4</v>
+        <v>22267</v>
       </c>
       <c r="I44" t="n">
         <v>22604.20349794094</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.51</v>
+        <v>-3.57</v>
       </c>
       <c r="L44" t="n">
-        <v>1.95</v>
+        <v>4.38</v>
       </c>
       <c r="M44" t="n">
         <v>1.75</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H45" t="n">
-        <v>22370.95</v>
+        <v>22853.7</v>
       </c>
       <c r="I45" t="n">
         <v>22441.73641405274</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.47</v>
+        <v>-2.63</v>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="M45" t="n">
         <v>1.39</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H46" t="n">
-        <v>31198.4</v>
+        <v>30284.55</v>
       </c>
       <c r="I46" t="n">
         <v>31088.37766308058</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K46" t="n">
-        <v>36.51</v>
+        <v>32.51</v>
       </c>
       <c r="L46" t="n">
         <v>1.46</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H47" t="n">
-        <v>30565.5</v>
+        <v>33089.05</v>
       </c>
       <c r="I47" t="n">
         <v>32090.76859151585</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.93</v>
+        <v>-9.26</v>
       </c>
       <c r="L47" t="n">
-        <v>3.31</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0.68</v>
+        <v>8.26</v>
       </c>
       <c r="O47" t="n">
         <v>-2.93</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.09</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H48" t="n">
-        <v>34804.6</v>
+        <v>34229.25</v>
       </c>
       <c r="I48" t="n">
         <v>34463.30540809556</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K48" t="n">
-        <v>5.18</v>
+        <v>3.45</v>
       </c>
       <c r="L48" t="n">
         <v>6.6</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.16</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H49" t="n">
-        <v>33459.25</v>
+        <v>33922.4</v>
       </c>
       <c r="I49" t="n">
         <v>33780.00573496405</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K49" t="n">
-        <v>2.25</v>
+        <v>0.9</v>
       </c>
       <c r="L49" t="n">
         <v>2.55</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.75</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H50" t="n">
-        <v>35079.2</v>
+        <v>34415.45</v>
       </c>
       <c r="I50" t="n">
         <v>34489.3935225969</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>3.41</v>
+        <v>1.45</v>
       </c>
       <c r="L50" t="n">
         <v>1.91</v>
@@ -3291,7 +3890,7 @@
         <v>1.91</v>
       </c>
       <c r="N50" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O50" t="n">
         <v>1.38</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44420</v>
+        <v>44421</v>
       </c>
       <c r="H51" t="n">
-        <v>35937.05</v>
+        <v>36169.35</v>
       </c>
       <c r="I51" t="n">
         <v>36072.71146154553</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.42</v>
+        <v>-5.1</v>
       </c>
       <c r="L51" t="n">
         <v>5.53</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.24</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H52" t="n">
-        <v>39508.95</v>
+        <v>39115.6</v>
       </c>
       <c r="I52" t="n">
         <v>39169.35202948152</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K52" t="n">
-        <v>9.23</v>
+        <v>8.15</v>
       </c>
       <c r="L52" t="n">
         <v>3.74</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.11</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H53" t="n">
-        <v>36840.15</v>
+        <v>37695.9</v>
       </c>
       <c r="I53" t="n">
         <v>36921.55795863635</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K53" t="n">
-        <v>5.82</v>
+        <v>3.63</v>
       </c>
       <c r="L53" t="n">
         <v>2.67</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.65</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H54" t="n">
-        <v>37392.05</v>
+        <v>35228.1</v>
       </c>
       <c r="I54" t="n">
         <v>36785.84871221876</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-6.55</v>
       </c>
       <c r="L54" t="n">
-        <v>3.5</v>
+        <v>7.17</v>
       </c>
       <c r="M54" t="n">
-        <v>2.26</v>
+        <v>3.49</v>
       </c>
       <c r="N54" t="n">
-        <v>4.18</v>
+        <v>5.79</v>
       </c>
       <c r="O54" t="n">
         <v>2.32</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.06</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H55" t="n">
-        <v>35748.25</v>
+        <v>36428.55</v>
       </c>
       <c r="I55" t="n">
         <v>36103.45136113906</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.48</v>
+        <v>-3.41</v>
       </c>
       <c r="L55" t="n">
         <v>4.2</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.51</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H56" t="n">
-        <v>36163.75</v>
+        <v>35264.55</v>
       </c>
       <c r="I56" t="n">
         <v>35730.20033091371</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.73</v>
+        <v>-3.2</v>
       </c>
       <c r="L56" t="n">
         <v>3.88</v>
@@ -3633,7 +4304,7 @@
         <v>1.68</v>
       </c>
       <c r="N56" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="O56" t="n">
         <v>1.9</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.64</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H57" t="n">
-        <v>35613.3</v>
+        <v>35826.95</v>
       </c>
       <c r="I57" t="n">
         <v>35817.19233819209</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.99</v>
+        <v>-1.59</v>
       </c>
       <c r="L57" t="n">
         <v>2.96</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.75</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H58" t="n">
-        <v>34483.8</v>
+        <v>33405.85</v>
       </c>
       <c r="I58" t="n">
         <v>33767.03094666647</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.75</v>
+        <v>-6.76</v>
       </c>
       <c r="L58" t="n">
-        <v>4.13</v>
+        <v>7.3</v>
       </c>
       <c r="M58" t="n">
-        <v>1.14</v>
+        <v>2.19</v>
       </c>
       <c r="N58" t="n">
-        <v>1.71</v>
+        <v>3.13</v>
       </c>
       <c r="O58" t="n">
         <v>0.6</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.36</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H59" t="n">
-        <v>34324.25</v>
+        <v>34920.3</v>
       </c>
       <c r="I59" t="n">
         <v>34619.04770961787</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.75</v>
+        <v>-4.53</v>
       </c>
       <c r="L59" t="n">
-        <v>2.94</v>
+        <v>4.67</v>
       </c>
       <c r="M59" t="n">
         <v>1.48</v>
       </c>
       <c r="N59" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
         <v>-3.13</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.47</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H60" t="n">
-        <v>40630.6</v>
+        <v>39546.25</v>
       </c>
       <c r="I60" t="n">
         <v>39555.33040802687</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K60" t="n">
-        <v>16.35</v>
+        <v>13.25</v>
       </c>
       <c r="L60" t="n">
         <v>1.31</v>
@@ -3861,7 +4580,7 @@
         <v>2.25</v>
       </c>
       <c r="N60" t="n">
-        <v>1.82</v>
+        <v>2.67</v>
       </c>
       <c r="O60" t="n">
         <v>1.74</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.64</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H61" t="n">
-        <v>39920.45</v>
+        <v>40318.75</v>
       </c>
       <c r="I61" t="n">
         <v>40219.35747284223</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.95</v>
+        <v>-1.95</v>
       </c>
       <c r="L61" t="n">
         <v>2.48</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H62" t="n">
-        <v>43359.5</v>
+        <v>42617.95</v>
       </c>
       <c r="I62" t="n">
         <v>42938.96863046256</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K62" t="n">
-        <v>7.54</v>
+        <v>5.7</v>
       </c>
       <c r="L62" t="n">
         <v>1.17</v>
@@ -3975,7 +4718,7 @@
         <v>0.77</v>
       </c>
       <c r="N62" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.42</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45026</v>
+        <v>45027</v>
       </c>
       <c r="H63" t="n">
-        <v>40834.65</v>
+        <v>41366.5</v>
       </c>
       <c r="I63" t="n">
         <v>41105.93590670836</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K63" t="n">
-        <v>4.18</v>
+        <v>2.94</v>
       </c>
       <c r="L63" t="n">
         <v>2.34</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.2</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H64" t="n">
-        <v>44995.7</v>
+        <v>44513.45</v>
       </c>
       <c r="I64" t="n">
         <v>44702.73682707026</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K64" t="n">
-        <v>8.77</v>
+        <v>7.61</v>
       </c>
       <c r="L64" t="n">
         <v>0.91</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>3.84</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H65" t="n">
-        <v>44878.35</v>
+        <v>45156.4</v>
       </c>
       <c r="I65" t="n">
         <v>45148.61779054233</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.82</v>
+        <v>-1.44</v>
       </c>
       <c r="L65" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M65" t="n">
         <v>0.54</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>3.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H66" t="n">
-        <v>45384.6</v>
+        <v>44623.85</v>
       </c>
       <c r="I66" t="n">
         <v>44777.99681223196</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" t="n">
-        <v>0.51</v>
+        <v>-1.18</v>
       </c>
       <c r="L66" t="n">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="M66" t="n">
         <v>1.06</v>
       </c>
       <c r="N66" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="O66" t="n">
         <v>0.62</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.12</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="H67" t="n">
-        <v>43820.1</v>
+        <v>43996.65</v>
       </c>
       <c r="I67" t="n">
         <v>43919.43174618245</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K67" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="L67" t="n">
         <v>1.46</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>2.92</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H68" t="n">
-        <v>48125.1</v>
+        <v>46064.45</v>
       </c>
       <c r="I68" t="n">
         <v>46793.10395864017</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K68" t="n">
-        <v>9.380000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="L68" t="n">
         <v>1.74</v>
       </c>
       <c r="M68" t="n">
-        <v>1.14</v>
+        <v>3.22</v>
       </c>
       <c r="N68" t="n">
-        <v>1.47</v>
+        <v>4.28</v>
       </c>
       <c r="O68" t="n">
         <v>0.4</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.56</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="H69" t="n">
-        <v>46120.9</v>
+        <v>47286.9</v>
       </c>
       <c r="I69" t="n">
         <v>47143.87501414356</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.12</v>
+        <v>-2.65</v>
       </c>
       <c r="L69" t="n">
         <v>2.82</v>
@@ -4374,7 +5201,7 @@
         <v>0.95</v>
       </c>
       <c r="N69" t="n">
-        <v>1.39</v>
+        <v>2.53</v>
       </c>
       <c r="O69" t="n">
         <v>-4.28</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.68</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H70" t="n">
-        <v>47484.8</v>
+        <v>47069.45</v>
       </c>
       <c r="I70" t="n">
         <v>47371.63964652875</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K70" t="n">
-        <v>0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="L70" t="n">
         <v>3.08</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>4.27</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H71" t="n">
-        <v>48201.05</v>
+        <v>49424.05</v>
       </c>
       <c r="I71" t="n">
         <v>48955.05632087123</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.4</v>
+        <v>-5</v>
       </c>
       <c r="L71" t="n">
-        <v>3.42</v>
+        <v>5.11</v>
       </c>
       <c r="M71" t="n">
         <v>1.2</v>
       </c>
       <c r="N71" t="n">
-        <v>1.07</v>
+        <v>2.54</v>
       </c>
       <c r="O71" t="n">
         <v>-0.87</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>5.03</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H72" t="n">
-        <v>48021.1</v>
+        <v>47487.9</v>
       </c>
       <c r="I72" t="n">
         <v>47620.50651314438</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.84</v>
+        <v>-3.92</v>
       </c>
       <c r="L72" t="n">
-        <v>3.18</v>
+        <v>4.01</v>
       </c>
       <c r="M72" t="n">
         <v>0.33</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>4.93</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H73" t="n">
-        <v>48983.95</v>
+        <v>50979.95</v>
       </c>
       <c r="I73" t="n">
         <v>49419.06585787926</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.15</v>
+        <v>-7.35</v>
       </c>
       <c r="L73" t="n">
-        <v>4.63</v>
+        <v>7.68</v>
       </c>
       <c r="M73" t="n">
-        <v>0.54</v>
+        <v>3.89</v>
       </c>
       <c r="N73" t="n">
-        <v>2.06</v>
+        <v>4.07</v>
       </c>
       <c r="O73" t="n">
         <v>-1.11</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.18</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H74" t="n">
-        <v>50979.95</v>
+        <v>46928.6</v>
       </c>
       <c r="I74" t="n">
         <v>48336.75485384146</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>-7.95</v>
       </c>
       <c r="L74" t="n">
-        <v>1.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O74" t="n">
         <v>4.07</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>10.58</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45467</v>
+        <v>45468</v>
       </c>
       <c r="H75" t="n">
-        <v>51703.95</v>
+        <v>52606</v>
       </c>
       <c r="I75" t="n">
         <v>51891.63313154268</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K75" t="n">
-        <v>-10.18</v>
+        <v>-12.1</v>
       </c>
       <c r="L75" t="n">
-        <v>10.72</v>
+        <v>12.4</v>
       </c>
       <c r="M75" t="n">
         <v>1.19</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>5.77</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H76" t="n">
-        <v>51350.15</v>
+        <v>50092.1</v>
       </c>
       <c r="I76" t="n">
         <v>50690.99108758482</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.39</v>
+        <v>-4.78</v>
       </c>
       <c r="L76" t="n">
-        <v>4.12</v>
+        <v>5.49</v>
       </c>
       <c r="M76" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="N76" t="n">
-        <v>0.96</v>
+        <v>2.45</v>
       </c>
       <c r="O76" t="n">
         <v>1.74</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>4.94</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H77" t="n">
-        <v>51772.4</v>
+        <v>51938.05</v>
       </c>
       <c r="I77" t="n">
         <v>51895.43350977891</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.35</v>
+        <v>-3.69</v>
       </c>
       <c r="L77" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="M77" t="n">
         <v>1.08</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>3.33</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H78" t="n">
-        <v>52922.6</v>
+        <v>51845.2</v>
       </c>
       <c r="I78" t="n">
         <v>52699.34239111573</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>1.9</v>
+        <v>-0.18</v>
       </c>
       <c r="L78" t="n">
         <v>0.57</v>
       </c>
       <c r="M78" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="N78" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="O78" t="n">
         <v>0.32</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>4.12</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H79" t="n">
-        <v>52109</v>
+        <v>52695.75</v>
       </c>
       <c r="I79" t="n">
         <v>52521.1661746413</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.51</v>
+        <v>-1.64</v>
       </c>
       <c r="L79" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="n">
         <v>1.78</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>4.44</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H80" t="n">
-        <v>51575.7</v>
+        <v>50759.2</v>
       </c>
       <c r="I80" t="n">
         <v>51552.90201780714</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.13</v>
+        <v>-3.67</v>
       </c>
       <c r="L80" t="n">
-        <v>2.72</v>
+        <v>3.96</v>
       </c>
       <c r="M80" t="n">
         <v>1.36</v>
       </c>
       <c r="N80" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="O80" t="n">
         <v>1.13</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>5.11</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H81" t="n">
-        <v>50157.95</v>
+        <v>50343.05</v>
       </c>
       <c r="I81" t="n">
         <v>50320.78608931672</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K81" t="n">
-        <v>1.18</v>
+        <v>0.82</v>
       </c>
       <c r="L81" t="n">
         <v>2.4</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>4.21</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H82" t="n">
-        <v>48344.7</v>
+        <v>48114.3</v>
       </c>
       <c r="I82" t="n">
         <v>48298.1744313446</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.97</v>
+        <v>-4.43</v>
       </c>
       <c r="L82" t="n">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="M82" t="n">
         <v>0.74</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>4.12</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H83" t="n">
-        <v>49314.5</v>
+        <v>49702.6</v>
       </c>
       <c r="I83" t="n">
         <v>49526.85746633085</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.49</v>
+        <v>-3.3</v>
       </c>
       <c r="L83" t="n">
-        <v>2.67</v>
+        <v>3.52</v>
       </c>
       <c r="M83" t="n">
         <v>0.91</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>3.62</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H84" t="n">
-        <v>55961.95</v>
+        <v>55617.6</v>
       </c>
       <c r="I84" t="n">
         <v>55763.89558918131</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K84" t="n">
-        <v>12.59</v>
+        <v>11.9</v>
       </c>
       <c r="L84" t="n">
         <v>1.1</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>6</v>
+      </c>
+      <c r="U84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>3.26</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H85" t="n">
-        <v>55147.6</v>
+        <v>55493.3</v>
       </c>
       <c r="I85" t="n">
         <v>55345.21452249736</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K85" t="n">
-        <v>0.85</v>
+        <v>0.22</v>
       </c>
       <c r="L85" t="n">
         <v>0.97</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>2.56</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H86" t="n">
-        <v>54976.2</v>
+        <v>54389.35</v>
       </c>
       <c r="I86" t="n">
         <v>54413.6881669877</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.93</v>
+        <v>-1.99</v>
       </c>
       <c r="L86" t="n">
-        <v>1.06</v>
+        <v>2.13</v>
       </c>
       <c r="M86" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="N86" t="n">
-        <v>0.7</v>
+        <v>1.07</v>
       </c>
       <c r="O86" t="n">
         <v>0.63</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5379,22 +6422,22 @@
         <v>2.86</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H87" t="n">
-        <v>55589.25</v>
+        <v>56104.85</v>
       </c>
       <c r="I87" t="n">
         <v>55803.19778482559</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K87" t="n">
-        <v>-2.21</v>
+        <v>-3.15</v>
       </c>
       <c r="L87" t="n">
-        <v>2.26</v>
+        <v>3.26</v>
       </c>
       <c r="M87" t="n">
         <v>0.45</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,19 +6491,19 @@
         <v>2.86</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H88" t="n">
-        <v>59404.2</v>
+        <v>58800.3</v>
       </c>
       <c r="I88" t="n">
         <v>58865.31046116025</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K88" t="n">
-        <v>5.88</v>
+        <v>4.8</v>
       </c>
       <c r="L88" t="n">
         <v>0.67</v>
@@ -5457,7 +6512,7 @@
         <v>0.57</v>
       </c>
       <c r="N88" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="O88" t="n">
         <v>0.93</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>4</v>
+      </c>
+      <c r="U88" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -5493,19 +6560,19 @@
         <v>3.09</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H89" t="n">
-        <v>60120.55</v>
+        <v>60669.35</v>
       </c>
       <c r="I89" t="n">
         <v>60617.09807253024</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K89" t="n">
-        <v>-2.25</v>
+        <v>-3.18</v>
       </c>
       <c r="L89" t="n">
         <v>5.04</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,28 +6629,28 @@
         <v>4.34</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H90" t="n">
-        <v>59839.65</v>
+        <v>58755.25</v>
       </c>
       <c r="I90" t="n">
         <v>59170.03250366158</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K90" t="n">
-        <v>-1.37</v>
+        <v>-3.15</v>
       </c>
       <c r="L90" t="n">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="M90" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="N90" t="n">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="O90" t="n">
         <v>0.91</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,28 +6698,28 @@
         <v>4.17</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H91" t="n">
-        <v>52716.25</v>
+        <v>55703.9</v>
       </c>
       <c r="I91" t="n">
         <v>55112.35887060154</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K91" t="n">
-        <v>10.28</v>
+        <v>5.19</v>
       </c>
       <c r="L91" t="n">
         <v>0.88</v>
       </c>
       <c r="M91" t="n">
-        <v>2.3</v>
+        <v>4.15</v>
       </c>
       <c r="N91" t="n">
-        <v>2.33</v>
+        <v>5.67</v>
       </c>
       <c r="O91" t="n">
         <v>-1.81</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5664,28 +6767,28 @@
         <v>9.35</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H92" t="n">
-        <v>54439.9</v>
+        <v>53555.2</v>
       </c>
       <c r="I92" t="n">
         <v>53700.70039814401</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K92" t="n">
-        <v>-2.27</v>
+        <v>-3.86</v>
       </c>
       <c r="L92" t="n">
-        <v>2.66</v>
+        <v>4.03</v>
       </c>
       <c r="M92" t="n">
         <v>2.27</v>
       </c>
       <c r="N92" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O92" t="n">
         <v>5.67</v>
@@ -5694,7 +6797,19 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5721,28 +6836,28 @@
         <v>6.15</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H93" t="n">
-        <v>55176.75</v>
+        <v>56814.8</v>
       </c>
       <c r="I93" t="n">
         <v>55933.46964473145</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K93" t="n">
-        <v>-3.03</v>
+        <v>-6.09</v>
       </c>
       <c r="L93" t="n">
-        <v>3.82</v>
+        <v>6.18</v>
       </c>
       <c r="M93" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="N93" t="n">
-        <v>2.29</v>
+        <v>2.97</v>
       </c>
       <c r="O93" t="n">
         <v>-1.63</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5778,19 +6905,19 @@
         <v>5.9</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H94" t="n">
-        <v>56777.55</v>
+        <v>56295.55</v>
       </c>
       <c r="I94" t="n">
         <v>56380.40367612209</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="L94" t="n">
         <v>1.92</v>
@@ -5808,7 +6935,19 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>4</v>
+      </c>
+      <c r="U94" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -5859,6 +6998,14 @@
       <c r="Q95" t="n">
         <v>33</v>
       </c>
+      <c r="R95" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10817,7 +11964,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.2</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="6">
@@ -10827,7 +11974,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -10837,7 +11984,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -10847,7 +11994,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10857,7 +12004,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -10867,7 +12014,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85.8</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="11">
@@ -10877,7 +12024,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -10887,7 +12034,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10897,7 +12044,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.9</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="14">
@@ -10907,7 +12054,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="15">
@@ -10917,7 +12064,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -10927,7 +12074,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.47</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="17">
@@ -10937,7 +12084,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36.51</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="18">
@@ -10947,7 +12094,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.2</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="19">
@@ -10957,7 +12104,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.03</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="20">
@@ -10967,7 +12114,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="21">
@@ -10977,7 +12124,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.72</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="22">
@@ -10987,7 +12134,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -11007,7 +12154,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="25">
@@ -11027,7 +12174,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.27</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="27">
@@ -11047,7 +12194,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
